--- a/outputs/599-9.xlsx
+++ b/outputs/599-9.xlsx
@@ -179,20 +179,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -388,240 +392,240 @@
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="0" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="0" t="s">
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>44044</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>44045</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="K4" s="1" t="n">
+      <c r="G4" s="2"/>
+      <c r="K4" s="2" t="n">
         <v>44046</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>44047</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>44047</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>44048</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>44048</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>44049</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>44049</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="2" t="n">
         <v>44050</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>44050</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="K9" s="1" t="n">
+      <c r="G9" s="2"/>
+      <c r="K9" s="2" t="n">
         <v>44051</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="2" t="n">
         <v>44052</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>44052</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="2" t="n">
         <v>44053</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>44053</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="2" t="n">
         <v>44054</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>44054</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="2" t="n">
         <v>44055</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>44055</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="G14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="2" t="n">
         <v>44057</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>44057</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="2" t="n">
         <v>44058</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>44058</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="2" t="n">
         <v>44059</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>44059</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="2" t="n">
         <v>44060</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>44060</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="2" t="n">
         <v>44061</v>
       </c>
-      <c r="K19" s="1" t="n">
+      <c r="K19" s="2" t="n">
         <v>44061</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -645,244 +649,244 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="0" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="0" t="s">
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>44044</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>44045</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="K4" s="1" t="n">
+      <c r="G4" s="2"/>
+      <c r="K4" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>44047</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>44047</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>44048</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>44048</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>44049</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>44049</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="2" t="n">
         <v>44050</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="K8" s="2" t="n">
         <v>44050</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="K9" s="1" t="n">
+      <c r="G9" s="2"/>
+      <c r="K9" s="2" t="n">
         <v>44051</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="2" t="n">
         <v>44052</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="K10" s="2" t="n">
         <v>44052</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="2" t="n">
         <v>44053</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="K11" s="2" t="n">
         <v>44053</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="2" t="n">
         <v>44054</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="K12" s="2" t="n">
         <v>44054</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="2" t="n">
         <v>44055</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="K13" s="2" t="n">
         <v>44055</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="0" t="s">
+      <c r="G14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="2" t="n">
         <v>44057</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="K15" s="2" t="n">
         <v>44057</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="2" t="n">
         <v>44058</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="K16" s="2" t="n">
         <v>44058</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="2" t="n">
         <v>44059</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="K17" s="2" t="n">
         <v>44059</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="2" t="n">
         <v>44060</v>
       </c>
-      <c r="K18" s="1" t="n">
+      <c r="K18" s="2" t="n">
         <v>44060</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="2" t="n">
         <v>44061</v>
       </c>
-      <c r="K19" s="1" t="n">
+      <c r="K19" s="2" t="n">
         <v>44061</v>
       </c>
-      <c r="L19" s="0" t="s">
+      <c r="L19" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
     </row>
